--- a/r4-ELGA-e-Medikation-relevantes-Profil-ergaenzen/ValueSet-ElgaListEntryFlagVS.xlsx
+++ b/r4-ELGA-e-Medikation-relevantes-Profil-ergaenzen/ValueSet-ElgaListEntryFlagVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:01:21+00:00</t>
+    <t>2026-04-20T08:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
